--- a/important_mails_2026-10-24.xlsx
+++ b/important_mails_2026-10-24.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H246"/>
+  <dimension ref="A1:H249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,178 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 22 Oct 2026 05:06:24 +0000</t>
+          <t>Sat, 24 Oct 2026 00:43:21 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>FBA reimbursement notification</t>
+          <t>Votre paiement est en cours</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+This title will display on mobile devices
+ Félicitations ! Votre paiement est en cours et arrivera sous peu.
+ Tentative de versement
+Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous 3 à 5 jours.
+Le 10/24/26 00:43 CEST, nous avons effectué un virement d’un montant de €
+ 61.41 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
+ Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
+ Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
+ Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de période.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 24 Oct 2026 04:18:18 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-11-05</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-11-05 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0GYPZ58JY Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 24 Oct 2026 04:12:00 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- uncUgm1HCf
+ Unsellable Products:
+- FNSKU: B0DRC8LPGS Quantity: 1
+- FNSKU: X0023C0TBV Quantity: 2
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 22 Oct 2026 05:06:24 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -530,39 +687,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 22:08:46 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -578,39 +735,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 05:28:28 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (bGwh+PF8WM)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -635,39 +792,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 23:34:06 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -688,39 +845,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:10:28 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -734,39 +891,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 07:37:41 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xqa4kwx264)</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -786,39 +943,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 05:04:59 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -834,39 +991,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Sun, 18 Oct 2026 14:44:50 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -889,87 +1046,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 17 Oct 2026 04:53:56 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 20 Oct 2026 14:23:03 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -989,39 +1098,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 07:34:34 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -1041,39 +1150,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 05:06:54 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"sell.amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Ocean shipping from China to Europe live on Amazon SEND</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Simplified ocean shipping from China to Europe with Amazon SEND
@@ -1092,39 +1201,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 22 Oct 2026 12:27:51 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -1144,39 +1253,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Thu, 22 Oct 2026 01:13:47 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1194,39 +1303,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 01:09:36 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1244,39 +1353,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:10:52 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1295,39 +1404,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:09:27 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1346,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Thu, 22 Oct 2026 13:30:07 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 9/2026</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 9/2026
  96
@@ -1401,39 +1510,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 14:23:14 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace UAE &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Prepare for UAE e-invoicing by January 1, 2027</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon Services
@@ -1474,39 +1583,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 14:12:44 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1521,39 +1630,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 21 Oct 2026 05:01:04 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -1574,39 +1683,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:21:18 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Prepare now for U.S. regulatory import changes</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Upcoming customs changes may affect your U.S. imports. Check your Importer of Record status and review your options today.
@@ -1620,39 +1729,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 17:08:31 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Envía documentos de cumplimiento normativo del producto para evitar que se retiren los listados
@@ -1666,39 +1775,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 08:00:21 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Update to FBA and MCF EU fuel and logistics-related surcharge</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Update to FBA and MCF EU fuel and logistics-related surcharge
  96
@@ -1711,91 +1820,40 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 17 Oct 2026 01:52:40 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
- Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
- Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
- Skicka in information om överensstämmelse
- Skicka in information om överensstämmelse
- Hur återaktiverar jag mina produktposter?
- Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
--
- Gå till sidan Kontostatus .
-- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
-- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
-- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Tue, 20 Oct 2026 08:30:54 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13389411022]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13389411022]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -1813,63 +1871,10 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 17 Oct 2026 04:18:17 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-10-29</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-29 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRCB74YN Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
-        </is>
-      </c>
-    </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>货件/库存类</t>
+          <t>其他风险类</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1884,132 +1889,21 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sat, 17 Oct 2026 04:16:43 +0000</t>
+          <t>Mon, 19 Oct 2026 17:08:31 +0000</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Create FBA removal order by 2026-10-29</t>
+          <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated removals of unfulfillable inventory
- Required removals: First notification
- Required removals: First notification
- Hello,
-Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-29 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
-Unsellable products:
-- FNSKU: B0DRCC2H56 Quantity: 1
-- FNSKU: B0DRCF83VZ Quantity: 1
-- FNSKU: B0GYPZ58JY Quantity: 2
- Why is this happening?
-This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
-We leveraged a combination of automated means to identify this issue and make this decision.
- How do I address this?
-Follow these steps to manage your unsellable inventory:
-- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
-- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
- To avoid future manual inventory removal orde</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 17 Oct 2026 03:57:58 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- kE9xVgxTCU
- Unsellable Products:
-- FNSKU: X0022I4RM3 Quantity: 1
-- FNSKU: X0023C0TBV Quantity: 2
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 19 Oct 2026 17:08:31 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -2023,39 +1917,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 19 Oct 2026 14:07:48 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -2084,39 +1978,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 15 Oct 2026 05:01:35 +0000</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 04:53:56 +0000</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2132,39 +2026,87 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 15 Oct 2026 05:01:35 +0000</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 16:23:15 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2185,39 +2127,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 05:11:00 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2233,39 +2175,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 17:44:30 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xqa6kjy120)</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2285,39 +2227,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:11:27 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2333,39 +2275,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 09:31:41 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2381,39 +2323,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 04:46:33 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2429,39 +2371,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 14:54:13 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Amazon.ca" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -2482,39 +2424,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 04:49:48 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2530,39 +2472,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 00:57:30 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -2580,39 +2522,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 05:03:27 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2628,39 +2570,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 16:07:57 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 As a valued Multichannel Fulfillment (MCF) managed customer, we are interested in learning about your program feedback including new features that may benefit your business. This may help us understand how we can better meet your business needs and continue to improve the customer experience.
@@ -2674,39 +2616,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:17:16 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2722,39 +2664,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 04:57:40 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2770,39 +2712,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 17:10:17 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2823,39 +2765,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 04:56:42 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2871,39 +2813,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 04:48:02 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2919,39 +2861,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 03:23:37 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Jl40SY3EId)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2971,39 +2913,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 19:30:09 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4sQeBGpWIe)</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3023,39 +2965,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 09:21:47 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3071,39 +3013,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:14:04 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3119,39 +3061,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 05:02:53 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3167,39 +3109,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 23:20:30 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cENUYoUvou)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3224,39 +3166,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 04:48:00 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3272,39 +3214,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 16:39:11 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3325,39 +3267,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 25 Sep 2026 04:50:51 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3373,39 +3315,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 04:54:38 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3421,39 +3363,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 16:43:27 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7iKN0D3u4y)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3473,39 +3415,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 05:28:45 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Amazon.it" &lt;store-news@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Il tuo carrello chiama</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.it/gp/cart/view.html?ref_=cor
 Tappetino ignifugo, 40 x 60 cm, resistente al calore, per friggitrice, protezione dal calore, protezione antincendio, protezione da piano di lavoro, antiscivolo e impermeabile
@@ -3526,39 +3468,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>KYC审核类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 05:15:33 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 145 PCS Eisenbahn Elektrisch Cube Track, 3D Schwerkrafttrotzendes Zug Set, DIY Zugstrecken Spielzeug, STEM Lernspielzeug &amp;amp; Geschenkidee für Kinder 3–8 Jahre, Kreatives Bauen Spielzeug
@@ -3579,39 +3521,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -3631,39 +3573,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 17:11:44 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3683,39 +3625,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 12:56:39 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -3739,39 +3681,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 14:51:24 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -3787,39 +3729,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Wed, 14 Oct 2026 17:02:54 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -3836,39 +3778,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 15:42:16 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3888,39 +3830,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 13:49:53 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3937,39 +3879,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 20:13:21 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Descargar el informe fiscal de China de abril a junio de 2026</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Ya puedes descargar tu declaración fiscal trimestral, que incluye datos como información de identidad, número de transacciones, ingresos y tarifas por servicios y comisiones.
@@ -3985,39 +3927,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:55:18 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January–March 2026</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report, which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4033,39 +3975,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 14:51:43 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4081,39 +4023,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 13:43:05 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>欧洲亚马逊 Payments &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>跨账户负余额调整</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4133,39 +4075,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:48:14 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europa &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Ajuste de saldo negativo en tus cuentas de Vender en Amazon</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4189,39 +4131,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 14:20:27 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4245,39 +4187,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 05:12:07 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>您的亚马逊卖家账户支付的余额</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 您的亚马逊卖家账户支付的余额
@@ -4306,39 +4248,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4358,39 +4300,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 23:31:42 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4410,39 +4352,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 14:51:16 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4458,39 +4400,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:36:40 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4510,39 +4452,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 13:33:11 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4562,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 00:41:51 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4614,39 +4556,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 12:37:44 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -4663,39 +4605,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 15 Oct 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4715,39 +4657,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 13 Oct 2026 01:19:09 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4765,39 +4707,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 17:16:17 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4815,39 +4757,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 08:57:55 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Reactivate your EU listings - GPSR compliance required</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Reactivate your EU listings - GPSR compliance required
@@ -4867,39 +4809,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Mon, 12 Oct 2026 01:16:04 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4917,39 +4859,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 17:11:11 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -4967,39 +4909,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 11 Oct 2026 16:03:12 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5017,39 +4959,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Fri, 9 Oct 2026 07:35:36 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -5076,39 +5018,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 13:20:34 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5126,39 +5068,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 12:56:57 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -5174,39 +5116,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 8 Oct 2026 11:25:17 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5224,39 +5166,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 13:15:21 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5274,39 +5216,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 11:16:06 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5324,39 +5266,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Wed, 7 Oct 2026 10:16:15 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5374,39 +5316,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 13:03:41 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -5422,39 +5364,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 10:13:01 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5472,39 +5414,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 22:52:24 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5522,39 +5464,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 5 Oct 2026 14:42:52 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5572,39 +5514,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 22:29:49 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5622,39 +5564,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 2 Oct 2026 19:40:11 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5672,39 +5614,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Wed, 30 Sep 2026 10:06:35 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5722,39 +5664,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 10:06:26 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -5772,39 +5714,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Tue, 29 Sep 2026 05:31:39 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>重要通知｜9月1日起，Pan-EU入库欧盟及直接发往法国的货件必须提供进口详情</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>未提供 MRN+EORI 将无法创建新货件，请在收货后 60 天内完成补全
 尊敬的 深圳市微海众信科技有限公司,
@@ -5832,39 +5774,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Mon, 28 Sep 2026 10:05:46 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -5883,39 +5825,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Sun, 27 Sep 2026 10:05:10 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -5934,39 +5876,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:10:33 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5984,39 +5926,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 01:07:50 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6034,39 +5976,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:57:06 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Zwrot kosztów zgodności z wymogami w zakresie opakowań w ramach ROP</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Dokończenie rejestracji w ramach ROP i uzyskanie częściowego zwrotu kosztów w Polsce
@@ -6083,39 +6025,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6133,39 +6075,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:28:03 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Få ersättning för kostnader för överensstämmelse med EPR-förpackningar</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Slutför EPR-registreringen och få en del av kostnaderna återbetalda i Sverige
@@ -6183,39 +6125,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:29 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6234,39 +6176,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Thu, 24 Sep 2026 10:08:17 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6282,6 +6224,57 @@
  If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
  For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
  To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 01:52:40 +0000</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Återaktivera dina EU-produktposter – GPSR-efterlevnad krävs
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats i våra butiker inom Europeiska unionen (EU) på grund av att information om överensstämmelse saknas. Den här åtgärden påverkar inte din kontostatus.
+ Du hittar exempel på de produktposter som har inaktiverats längst ner i detta e-postmeddelande, och hela listan finns på sidan Kontostatus. Granska de berörda produktposterna och nästa steg för att uppfylla kraven i Förordningen om allmän produktsäkerhet (GPSR) nedan.
+ Skicka in information om överensstämmelse
+ Skicka in information om överensstämmelse
+ Hur återaktiverar jag mina produktposter?
+ Om du vill återaktivera dina produktposter behöver du ange den efterfrågade GPSR-informationen om överensstämmelse genom att följa anvisningarna nedan:
+-
+ Gå till sidan Kontostatus .
+- Välj Lägg till filter och markera Produktpost borttagen i kolumnen Filtrera efter vidtagen åtgärd.
+- Klicka på Skicka in bredvid den inaktiverade produktposten och följ instruktionerna.
+- Följ stegen på Dolda produktposter för att åtgärda eventuella kvarstående problem med produktposter. Befintliga problem förhindrar att produktposter åter</t>
         </is>
       </c>
     </row>
@@ -12356,22 +12349,186 @@
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
+          <t>Sat, 17 Oct 2026 04:18:17 +0000</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-10-29</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr"/>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-29 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRCB74YN Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orders, set up Automated Unfulfillable Removals function in your FBA</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 04:16:43 +0000</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Create FBA removal order by 2026-10-29</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr"/>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated removals of unfulfillable inventory
+ Required removals: First notification
+ Required removals: First notification
+ Hello,
+Your FBA inventory listed below became unsellable in the past seven days. You must create a removal order by 2026-10-29 or these items will be disposed of. Removal fees will apply. Review the affected items and next steps below.
+Unsellable products:
+- FNSKU: B0DRCC2H56 Quantity: 1
+- FNSKU: B0DRCF83VZ Quantity: 1
+- FNSKU: B0GYPZ58JY Quantity: 2
+ Why is this happening?
+This action is required because these items are no longer in sellable condition in our fulfilment centres. According to our FBA Required Removals policy, all unsuitable units must be removed within 14 days of notification. To learn more, go to our FBA Required Removals policy .
+We leveraged a combination of automated means to identify this issue and make this decision.
+ How do I address this?
+Follow these steps to manage your unsellable inventory:
+- Check your complete list and quantity of unsellable items in the Manage FBA inventory .
+- Create a removal order (removal fees apply) by following the instructions in Remove inventory overview .
+ To avoid future manual inventory removal orde</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 17 Oct 2026 03:57:58 +0000</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Disposal order created for unsellable FBA inventory</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr"/>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>96
+Automated Removals of Unfulfillable Inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Final notice: Disposal order for your unfulfillable FBA inventory
+ Hello,
+You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
+ Why is this happening?
+This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
+ Removal order ID:
+- kE9xVgxTCU
+ Unsellable Products:
+- FNSKU: X0022I4RM3 Quantity: 1
+- FNSKU: X0023C0TBV Quantity: 2
+ For more information about the disposal order process, see Remove inventory from a fulfilment centre .
+ To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
+ The Fulfilment by Amazon Team
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferen</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
           <t>Thu, 15 Oct 2026 08:25:20 +0000</t>
         </is>
       </c>
-      <c r="E233" s="2" t="inlineStr">
+      <c r="E236" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F233" s="2" t="inlineStr">
+      <c r="F236" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on
  Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G233" s="2" t="inlineStr"/>
-      <c r="H233" s="2" t="inlineStr">
+      <c r="G236" s="2" t="inlineStr"/>
+      <c r="H236" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13389411022] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -12387,39 +12544,39 @@
         </is>
       </c>
     </row>
-    <row r="234">
-      <c r="A234" s="2" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B234" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C234" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D234" s="2" t="inlineStr">
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:51:55 +0000</t>
         </is>
       </c>
-      <c r="E234" s="2" t="inlineStr">
+      <c r="E237" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F234" s="2" t="inlineStr">
+      <c r="F237" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-22</t>
         </is>
       </c>
-      <c r="G234" s="2" t="inlineStr"/>
-      <c r="H234" s="2" t="inlineStr">
+      <c r="G237" s="2" t="inlineStr"/>
+      <c r="H237" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12441,39 +12598,39 @@
         </is>
       </c>
     </row>
-    <row r="235">
-      <c r="A235" s="2" t="inlineStr">
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B235" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C235" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D235" s="2" t="inlineStr">
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
         <is>
           <t>Sat, 10 Oct 2026 03:37:48 +0000</t>
         </is>
       </c>
-      <c r="E235" s="2" t="inlineStr">
+      <c r="E238" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F235" s="2" t="inlineStr">
+      <c r="F238" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G235" s="2" t="inlineStr"/>
-      <c r="H235" s="2" t="inlineStr">
+      <c r="G238" s="2" t="inlineStr"/>
+      <c r="H238" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12497,39 +12654,39 @@
         </is>
       </c>
     </row>
-    <row r="236">
-      <c r="A236" s="2" t="inlineStr">
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B236" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C236" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D236" s="2" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
         <is>
           <t>Tue, 6 Oct 2026 20:20:03 +0000</t>
         </is>
       </c>
-      <c r="E236" s="2" t="inlineStr">
+      <c r="E239" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F236" s="2" t="inlineStr">
+      <c r="F239" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G236" s="2" t="inlineStr"/>
-      <c r="H236" s="2" t="inlineStr">
+      <c r="G239" s="2" t="inlineStr"/>
+      <c r="H239" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -12545,39 +12702,39 @@
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="2" t="inlineStr">
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B237" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C237" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D237" s="2" t="inlineStr">
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
         <is>
           <t>Sun, 4 Oct 2026 20:33:01 +0000</t>
         </is>
       </c>
-      <c r="E237" s="2" t="inlineStr">
+      <c r="E240" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F237" s="2" t="inlineStr">
+      <c r="F240" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G237" s="2" t="inlineStr"/>
-      <c r="H237" s="2" t="inlineStr">
+      <c r="G240" s="2" t="inlineStr"/>
+      <c r="H240" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -12593,39 +12750,39 @@
         </is>
       </c>
     </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B238" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C238" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D238" s="2" t="inlineStr">
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
         <is>
           <t>Sat, 3 Oct 2026 03:07:33 +0000</t>
         </is>
       </c>
-      <c r="E238" s="2" t="inlineStr">
+      <c r="E241" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F238" s="2" t="inlineStr">
+      <c r="F241" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-15</t>
         </is>
       </c>
-      <c r="G238" s="2" t="inlineStr"/>
-      <c r="H238" s="2" t="inlineStr">
+      <c r="G241" s="2" t="inlineStr"/>
+      <c r="H241" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12649,39 +12806,39 @@
         </is>
       </c>
     </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:55:34 +0000</t>
         </is>
       </c>
-      <c r="E239" s="2" t="inlineStr">
+      <c r="E242" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F239" s="2" t="inlineStr">
+      <c r="F242" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G239" s="2" t="inlineStr"/>
-      <c r="H239" s="2" t="inlineStr">
+      <c r="G242" s="2" t="inlineStr"/>
+      <c r="H242" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -12704,39 +12861,39 @@
         </is>
       </c>
     </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="inlineStr">
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
         <is>
           <t>Sat, 26 Sep 2026 04:10:17 +0000</t>
         </is>
       </c>
-      <c r="E240" s="2" t="inlineStr">
+      <c r="E243" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F240" s="2" t="inlineStr">
+      <c r="F243" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-10-08</t>
         </is>
       </c>
-      <c r="G240" s="2" t="inlineStr"/>
-      <c r="H240" s="2" t="inlineStr">
+      <c r="G243" s="2" t="inlineStr"/>
+      <c r="H243" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -12760,39 +12917,39 @@
         </is>
       </c>
     </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="inlineStr">
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
         <is>
           <t>Wed, 23 Sep 2026 17:17:49 +0000</t>
         </is>
       </c>
-      <c r="E241" s="2" t="inlineStr">
+      <c r="E244" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F241" s="2" t="inlineStr">
+      <c r="F244" s="2" t="inlineStr">
         <is>
           <t>Remove aged, stranded, and unfulfillable inventory by 22nd Oct 2026</t>
         </is>
       </c>
-      <c r="G241" s="2" t="inlineStr"/>
-      <c r="H241" s="2" t="inlineStr">
+      <c r="G244" s="2" t="inlineStr"/>
+      <c r="H244" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -12807,39 +12964,39 @@
         </is>
       </c>
     </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="inlineStr">
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 02:02:21 +0000</t>
         </is>
       </c>
-      <c r="E242" s="2" t="inlineStr">
+      <c r="E245" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon Business &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F242" s="2" t="inlineStr">
+      <c r="F245" s="2" t="inlineStr">
         <is>
           <t>Earn new Business Discount badge for always-on visibility</t>
         </is>
       </c>
-      <c r="G242" s="2" t="inlineStr"/>
-      <c r="H242" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr"/>
+      <c r="H245" s="2" t="inlineStr">
         <is>
           <t>96
  New badge launches in two weeks - set your Business Price at least 5% below standard retail price to get started
@@ -12852,39 +13009,39 @@
         </is>
       </c>
     </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Fri, 16 Oct 2026 09:43:53 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E243" s="2" t="inlineStr">
+      <c r="E246" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F243" s="2" t="inlineStr">
+      <c r="F246" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G243" s="2" t="inlineStr"/>
-      <c r="H243" s="2" t="inlineStr">
+      <c r="G246" s="2" t="inlineStr"/>
+      <c r="H246" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -12913,39 +13070,39 @@
         </is>
       </c>
     </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 21:27:08 +0000</t>
         </is>
       </c>
-      <c r="E244" s="2" t="inlineStr">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F244" s="2" t="inlineStr">
+      <c r="F247" s="2" t="inlineStr">
         <is>
           <t>A passkey is required for account access starting in two weeks</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr"/>
-      <c r="H244" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr"/>
+      <c r="H247" s="2" t="inlineStr">
         <is>
           <t>96
  For security, set up passkey login to maintain account access
@@ -12961,39 +13118,39 @@
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 04:58:43 +0000</t>
         </is>
       </c>
-      <c r="E245" s="2" t="inlineStr">
+      <c r="E248" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F245" s="2" t="inlineStr">
+      <c r="F248" s="2" t="inlineStr">
         <is>
           <t>A returns experience customers actually like</t>
         </is>
       </c>
-      <c r="G245" s="2" t="inlineStr"/>
-      <c r="H245" s="2" t="inlineStr">
+      <c r="G248" s="2" t="inlineStr"/>
+      <c r="H248" s="2" t="inlineStr">
         <is>
           <t>96
  Faster resolutions for buyers, less friction for you.
@@ -13018,39 +13175,39 @@
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="inlineStr">
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
         <is>
           <t>Thu, 1 Oct 2026 00:17:41 +0000</t>
         </is>
       </c>
-      <c r="E246" s="2" t="inlineStr">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F246" s="2" t="inlineStr">
+      <c r="F249" s="2" t="inlineStr">
         <is>
           <t>View your US Q4-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr"/>
-      <c r="H246" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr"/>
+      <c r="H249" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q4-2026
